--- a/fleet_tally/samples/cash_sales_template.xlsx
+++ b/fleet_tally/samples/cash_sales_template.xlsx
@@ -454,14 +454,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Cash sales — Motor Spirit (petrol)  →  Tally voucher type “MS Cash” (CASH/MS/…)</t>
+          <t>Cash sales — Motor Spirit (petrol)  →  Tally voucher type “Cash MS” (numbered by date: Cash/MS/1Oct2026)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>One row per day: the litres sold for cash and that day's price per litre. Amount = Quantity × Price (rounded to paise). Leave a day out if nothing was sold.</t>
+          <t>One row per day (the voucher number is the date): the litres sold for cash and that day's price per litre. Amount = Quantity × Price (rounded to paise). Leave a day out if nothing was sold.</t>
         </is>
       </c>
     </row>

--- a/fleet_tally/samples/cash_sales_template.xlsx
+++ b/fleet_tally/samples/cash_sales_template.xlsx
@@ -684,14 +684,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Cash sales — High Speed Diesel  →  Tally voucher type “HSD CASH” (CASH/HSD/…)</t>
+          <t>Cash sales — High Speed Diesel  →  Tally voucher type “HSD CASH” (numbered by date: Cash/HSD/1Oct2026)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>One row per day: the litres sold for cash and that day's price per litre. Amount = Quantity × Price (rounded to paise). Leave a day out if nothing was sold.</t>
+          <t>One row per day (the voucher number is the date): the litres sold for cash and that day's price per litre. Amount = Quantity × Price (rounded to paise). Leave a day out if nothing was sold.</t>
         </is>
       </c>
     </row>
@@ -914,14 +914,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Cash sales — XtraGreen Diesel  →  Tally voucher type “XG CASH” (CASH/XG/…)</t>
+          <t>Cash sales — XtraGreen Diesel  →  Tally voucher type “XG CASH” (numbered by date: Cash/XG/1Oct2026)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>One row per day: the litres sold for cash and that day's price per litre. Amount = Quantity × Price (rounded to paise). Leave a day out if nothing was sold.</t>
+          <t>One row per day (the voucher number is the date): the litres sold for cash and that day's price per litre. Amount = Quantity × Price (rounded to paise). Leave a day out if nothing was sold.</t>
         </is>
       </c>
     </row>
